--- a/DIRECCIONES.xlsx
+++ b/DIRECCIONES.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jaime Saucedo\Documents\0. My info\Python\Mapa_Interactivo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE6265AB-F516-4196-996D-A6605D3F073A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78CD22CA-89C3-44ED-8A08-3F0DA4309793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$111:$T$111</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="1027">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="1072">
   <si>
     <t>Title</t>
   </si>
@@ -3036,19 +3033,46 @@
     <t>33 2490 6988</t>
   </si>
   <si>
-    <t>Anillo Vial II 10271, 76246 Segunda Secc. de Conín, Qro.</t>
+    <t>Norte 45 1016. Col Industrial Vallejo, cp. 09450. Azcapotzalco. CDMX.</t>
+  </si>
+  <si>
+    <t>19.486876967252908, -99.16117286050928</t>
   </si>
   <si>
     <t>Bodega</t>
   </si>
   <si>
-    <t>Antiguo Camino a Sta. María del Río 171, Rural la Esperanza, 78421 Pozos, S.L.P.</t>
-  </si>
-  <si>
-    <t>Av. Acero 27, Cd Industrial, 86010 Villahermosa, Tab.</t>
-  </si>
-  <si>
-    <t>Av. Centenario 54-148, Civac, 62550 Jiutepec, Mor</t>
+    <t>Cuauhtémoc 731-A, Zona urbana ejidal Santa María Aztahuacan, CP: 09570 Alcaldía Iztapalapa CDMX</t>
+  </si>
+  <si>
+    <t>19.354401332320144, -99.03895906051099</t>
+  </si>
+  <si>
+    <t>Riachuelo Serpentino 575, San José, Tláhuac, 13020 Ciudad de México, CDMX</t>
+  </si>
+  <si>
+    <t>19.280744596541197, -99.00072767400437</t>
+  </si>
+  <si>
+    <t>HUB_AGU_AGU</t>
+  </si>
+  <si>
+    <t>Av. P.º San Gerardo 146, 20342 San Gerardo, Ags.</t>
+  </si>
+  <si>
+    <t>21.80581744826868, -102.29407568931323</t>
+  </si>
+  <si>
+    <t>Lerdo de Tejada 449, int 3, col Centro , Colima, Colima, CP 28000</t>
+  </si>
+  <si>
+    <t>19.233807971607664, -103.72475021818431</t>
+  </si>
+  <si>
+    <t>Av. del Valle de Manzanares 1404, San Isidro Nte, 37510 León de los Aldama, Gto.</t>
+  </si>
+  <si>
+    <t>21.10742620589422, -101.64658084514404</t>
   </si>
   <si>
     <t>Av. de los Artesanos 5161,
@@ -3056,115 +3080,223 @@
 San Pedro Tlaquepaque, Jalisco.</t>
   </si>
   <si>
-    <t>Av. del Valle de Manzanares 1404, San Isidro Nte, 37510 León de los Aldama, Gto.</t>
-  </si>
-  <si>
-    <t>HUB_AGU_AGU</t>
-  </si>
-  <si>
-    <t>Av. P.º San Gerardo 146, 20342 San Gerardo, Ags.</t>
+    <t>20.58400481902223, -103.35789429928894</t>
+  </si>
+  <si>
+    <t>HUB_EDOMEX_TOLUCA</t>
+  </si>
+  <si>
+    <t>C. Industria Minera 602, Santa Ana Tlapaltitlán, 50160 Santa Ana Tlapaltitlán, Méx</t>
+  </si>
+  <si>
+    <t>19.302520619446586, -99.61104466051168</t>
+  </si>
+  <si>
+    <t>Av. del Peral 32, Joaquin Lopez Negrete, 54713 San Mateo Ixtacalco, Méx.</t>
+  </si>
+  <si>
+    <t>19.705410396488343, -99.18186697399885</t>
+  </si>
+  <si>
+    <t>Av. Centenario 54-148, Civac, 62550 Jiutepec, Mor</t>
+  </si>
+  <si>
+    <t>18.907621830764104, -99.16860136051672</t>
+  </si>
+  <si>
+    <t>HUB_NAYARIT_TEPIC</t>
+  </si>
+  <si>
+    <t>Cobalto 9, Microindustria, 63173 Tepic, Nay.</t>
+  </si>
+  <si>
+    <t>21.47459526122855, -104.852706118154</t>
+  </si>
+  <si>
+    <t>Prol. Lic. Gustavo Díaz Ordaz 310 B, Bosques del Nogalar. San Nicolas de los Garza, Monterrey Nuevo Leon</t>
+  </si>
+  <si>
+    <t>25.725167783232024, -100.27377470274129</t>
+  </si>
+  <si>
+    <t>C. Uranga 93, 72702 San Juan Cuautlancingo, Pue.</t>
+  </si>
+  <si>
+    <t>19.111799181770937, -98.26244956051406</t>
+  </si>
+  <si>
+    <t>Anillo Vial II 10271, 76246 Segunda Secc. de Conín, Qro.</t>
+  </si>
+  <si>
+    <t>20.57270908434535, -100.31304404515149</t>
   </si>
   <si>
     <t>C. Caliza 6, El Pedregal, 77536 Cancún, Q.R.</t>
   </si>
   <si>
-    <t>HUB_EDOMEX_TOLUCA</t>
-  </si>
-  <si>
-    <t>C. Industria Minera 602, Santa Ana Tlapaltitlán, 50160 Santa Ana Tlapaltitlán, Méx</t>
-  </si>
-  <si>
-    <t>C. Uranga 93, 72702 San Juan Cuautlancingo, Pue.</t>
-  </si>
-  <si>
-    <t>HUB_NAYARIT_TEPIC</t>
-  </si>
-  <si>
-    <t>Cobalto 9, Microindustria, 63173 Tepic, Nay.</t>
+    <t>21.13501654501374, -86.89735586048712</t>
+  </si>
+  <si>
+    <t>Antiguo Camino a Sta. María del Río 171, Rural la Esperanza, 78421 Pozos, S.L.P.</t>
+  </si>
+  <si>
+    <t>22.08711671708872, -100.87646381814494</t>
+  </si>
+  <si>
+    <t>HUB_SINALOA_CULIACAN</t>
+  </si>
+  <si>
+    <t>Libramiento No. 6301 pte., Bachigualato, 80140 Culiacán Rosales, Sin.</t>
+  </si>
+  <si>
+    <t>24.748667922875885, -107.45738807102278</t>
+  </si>
+  <si>
+    <t>Av. Acero 27, Cd Industrial, 86010 Villahermosa, Tab.</t>
+  </si>
+  <si>
+    <t>18.029792729223523, -92.90935857401952</t>
   </si>
   <si>
     <t>Cto. Colonias 891C, Obrera, 97260 Mérida, Yuc.</t>
   </si>
   <si>
-    <t>Cuauhtémoc 731-A, Zona urbana ejidal Santa María Aztahuacan, CP: 09570 Alcaldía Iztapalapa CDMX</t>
-  </si>
-  <si>
-    <t>Lerdo de Tejada 449, int 3, col Centro , Colima, Colima, CP 28000</t>
-  </si>
-  <si>
-    <t>HUB_SINALOA_CULIACAN</t>
-  </si>
-  <si>
-    <t>Libramiento No. 6301 pte., Bachigualato, 80140 Culiacán Rosales, Sin.</t>
-  </si>
-  <si>
-    <t>Norte 45 1016. Col Industrial Vallejo, cp. 09450. Azcapotzalco. CDMX.</t>
-  </si>
-  <si>
-    <t>Prol. Lic. Gustavo Díaz Ordaz 310 B, Bosques del Nogalar. San Nicolas de los Garza, Monterrey Nuevo Leon</t>
-  </si>
-  <si>
-    <t>Riachuelo Serpentino 575, San José, Tláhuac, 13020 Ciudad de México, CDMX</t>
-  </si>
-  <si>
-    <t>20.57270908434535, -100.31304404515149</t>
-  </si>
-  <si>
-    <t>22.08711671708872, -100.87646381814494</t>
-  </si>
-  <si>
-    <t>18.029792729223523, -92.90935857401952</t>
-  </si>
-  <si>
-    <t>18.907621830764104, -99.16860136051672</t>
-  </si>
-  <si>
-    <t>20.58400481902223, -103.35789429928894</t>
-  </si>
-  <si>
-    <t>21.10742620589422, -101.64658084514404</t>
-  </si>
-  <si>
-    <t>Av. del Peral 32, Joaquin Lopez Negrete, 54713 San Mateo Ixtacalco, Méx.</t>
-  </si>
-  <si>
-    <t>19.705410396488343, -99.18186697399885</t>
-  </si>
-  <si>
-    <t>21.80581744826868, -102.29407568931323</t>
-  </si>
-  <si>
-    <t>21.13501654501374, -86.89735586048712</t>
-  </si>
-  <si>
-    <t>19.302520619446586, -99.61104466051168</t>
-  </si>
-  <si>
-    <t>19.111799181770937, -98.26244956051406</t>
-  </si>
-  <si>
-    <t>21.47459526122855, -104.852706118154</t>
-  </si>
-  <si>
     <t>20.9412644841733, -89.64906944514635</t>
   </si>
   <si>
-    <t>19.354401332320144, -99.03895906051099</t>
-  </si>
-  <si>
-    <t>19.233807971607664, -103.72475021818431</t>
-  </si>
-  <si>
-    <t>24.748667922875885, -107.45738807102278</t>
-  </si>
-  <si>
-    <t>19.486876967252908, -99.16117286050928</t>
-  </si>
-  <si>
-    <t>25.725167783232024, -100.27377470274129</t>
-  </si>
-  <si>
-    <t>19.280744596541197, -99.00072767400437</t>
+    <t>ZCL | Alta de proveedor DSP Luis Antonio Luria Martínez</t>
+  </si>
+  <si>
+    <t>Apexphat</t>
+  </si>
+  <si>
+    <t>Luis Antonio Luria Martínez</t>
+  </si>
+  <si>
+    <t>LUML9709129L5</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/De+Los+Nogales+117,+Exhacienda+de+Bernardez,+98064+Guadalupe,+Zac./@22.7659678,-102.5447789,17z/data=!3m1!4b1!4m6!3m5!1s0x86824eb80ffabff5:0xa7eb870c2be92c23!8m2!3d22.7659629!4d-102.542204!16s%2Fg%2F11cshdv83_?entry=ttu&amp;g_ep=EgoyMDI2MDcyMi4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>De Los Nogales 117, Exhacienda de Bernardez, 98064 Guadalupe, Zac.</t>
+  </si>
+  <si>
+    <t>22.76609148812428, -102.54222546046284</t>
+  </si>
+  <si>
+    <t>ventas@apexpathway.com</t>
+  </si>
+  <si>
+    <t>4921246097</t>
+  </si>
+  <si>
+    <t>VER_ENLAINTE SOLUCIONES</t>
+  </si>
+  <si>
+    <t>Miguel Angel Flores Salgado</t>
+  </si>
+  <si>
+    <t>FOSM901219QM9</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Cuautla+-+Yautepec+de+Zaragoza+76,+San+Carlos,+Los+Arcos,+Mor./@18.8947237,-99.0359591,17z/data=!4m13!1m7!3m6!1s0x85ce72156b3047e3:0x4769b5f89d3d8e65!2sCuautla+-+Yautepec+de+Zaragoza+76,+San+Carlos,+Los+Arcos,+Mor.!3b1!8m2!3d18.8946867!4d-99.0335057!3m4!1s0x85ce72156b3047e3:0x4769b5f89d3d8e65!8m2!3d18.8946867!4d-99.0335057?entry=ttu&amp;g_ep=EgoyMDI2MDcyMi4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>Cuautla - Yautepec de Zaragoza 76, San Carlos, Los Arcos, Mor.</t>
+  </si>
+  <si>
+    <t>18.894901299312888, -99.0334807048269</t>
+  </si>
+  <si>
+    <t>m_salgado_m19@outlook.com</t>
+  </si>
+  <si>
+    <t>5611675171 / 5560342054</t>
+  </si>
+  <si>
+    <t>STAHUB_COCO_MIGUELFLORES_JIUTEPEC</t>
+  </si>
+  <si>
+    <t>NL | Alta DSP Maria Cristina Fernandez Ochoa</t>
+  </si>
+  <si>
+    <t>Virasat</t>
+  </si>
+  <si>
+    <t>Maria Cristina Fernandez Ochoa</t>
+  </si>
+  <si>
+    <t>FEOC7302076L1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Antonio+Pl.+521,+La+Luz,+67120+Guadalupe,+N.L./@25.7054642,-100.242557,17z/data=!3m1!4b1!4m6!3m5!1s0x8662eac05c1128c3:0x4cb64d6a4bcd5ddb!8m2!3d25.7054642!4d-100.2399821!16s%2Fg%2F11v0yk86ym?entry=ttu&amp;g_ep=EgoyMDI2MDcyMi4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>Antonio Pl. 521, La Luz, 67120 Guadalupe, N.L.</t>
+  </si>
+  <si>
+    <t>25.705686519644644, -100.23992845844732</t>
+  </si>
+  <si>
+    <t>virasatpaqueteria@outlook.com</t>
+  </si>
+  <si>
+    <t>8182871715 / 8147347008</t>
+  </si>
+  <si>
+    <t>CDMX| Alta de Proveedor JONATAN BARROS MARTINEZ DSP</t>
+  </si>
+  <si>
+    <t>Jonatan Barros Martinez</t>
+  </si>
+  <si>
+    <t>BAMJ9409136I2</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Calz.+Vallejo+651,+Magdalena+de+las+Salinas,+Gustavo+A.+Madero,+07760+Ciudad+de+M%C3%A9xico,+CDMX/@19.480811,-99.1510813,17z/data=!3m1!4b1!4m6!3m5!1s0x85d1f8559dbe6da1:0x21b4deb951289f36!8m2!3d19.480811!4d-99.1485064!16s%2Fg%2F11c0pvdmb3?entry=ttu&amp;g_ep=EgoyMDI2MDcyMi4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>Calz. Vallejo 651, Magdalena de las Salinas, Gustavo A. Madero, 07760 Ciudad de México, CDMX</t>
+  </si>
+  <si>
+    <t>19.48104361846981, -99.14850640274712</t>
+  </si>
+  <si>
+    <t>logisticadepuntoapuntojbsadecv@gmail.com</t>
+  </si>
+  <si>
+    <t>5517483173</t>
+  </si>
+  <si>
+    <t>MTY | Alta DSP Adrian Eduardo Gonzalez Gonzalez</t>
+  </si>
+  <si>
+    <t>RAWE LOGISTICS</t>
+  </si>
+  <si>
+    <t>Adrian Eduardo Gonzalez Gonzalez</t>
+  </si>
+  <si>
+    <t>GOGA9306283M3</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Calle+Av.+Henequ%C3%A9n+1709,+entre+calle+Jumanos+y+Puerto+Huelva,+32590+Ju%C3%A1rez,+Chih./@31.6114689,-106.3513044,17z/data=!3m1!4b1!4m6!3m5!1s0x86e767d5b0e573a9:0xf64627353699d1b7!8m2!3d31.6114644!4d-106.3487295!16s%2Fg%2F11jstp_y3r?entry=ttu&amp;g_ep=EgoyMDI2MDcyMi4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>Calle Av. Henequén 1709, entre calle Jumanos y Puerto Huelva, 32590 Juárez, Chih.</t>
+  </si>
+  <si>
+    <t>31.611592290877073, -106.34880460447233</t>
+  </si>
+  <si>
+    <t>aeg.gon9@gmail.com</t>
+  </si>
+  <si>
+    <t>6141395226</t>
+  </si>
+  <si>
+    <t>HUB_ZCL_ZCL</t>
   </si>
 </sst>
 </file>
@@ -3210,28 +3342,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3529,12 +3640,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S130"/>
+  <dimension ref="A1:S136"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="8" max="8" width="96" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="37.7109375" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -9331,10 +9438,10 @@
         <v>86</v>
       </c>
       <c r="H112" t="s">
-        <v>1004</v>
+        <v>984</v>
       </c>
       <c r="I112" t="s">
-        <v>1024</v>
+        <v>985</v>
       </c>
       <c r="M112">
         <v>19.486876967252901</v>
@@ -9343,9 +9450,9 @@
         <v>-99.161172860509197</v>
       </c>
       <c r="O112" t="s">
-        <v>985</v>
-      </c>
-      <c r="P112" s="1">
+        <v>986</v>
+      </c>
+      <c r="P112">
         <v>9450</v>
       </c>
       <c r="S112" t="s">
@@ -9357,10 +9464,10 @@
         <v>253</v>
       </c>
       <c r="H113" t="s">
-        <v>1000</v>
+        <v>987</v>
       </c>
       <c r="I113" t="s">
-        <v>1021</v>
+        <v>988</v>
       </c>
       <c r="M113">
         <v>19.354401332320101</v>
@@ -9369,9 +9476,9 @@
         <v>-99.038959060510905</v>
       </c>
       <c r="O113" t="s">
-        <v>985</v>
-      </c>
-      <c r="P113" s="1">
+        <v>986</v>
+      </c>
+      <c r="P113">
         <v>9570</v>
       </c>
       <c r="S113" t="s">
@@ -9383,10 +9490,10 @@
         <v>158</v>
       </c>
       <c r="H114" t="s">
-        <v>1006</v>
+        <v>989</v>
       </c>
       <c r="I114" t="s">
-        <v>1026</v>
+        <v>990</v>
       </c>
       <c r="M114">
         <v>19.280744596541101</v>
@@ -9395,9 +9502,9 @@
         <v>-99.000727674004295</v>
       </c>
       <c r="O114" t="s">
-        <v>985</v>
-      </c>
-      <c r="P114" s="1">
+        <v>986</v>
+      </c>
+      <c r="P114">
         <v>13020</v>
       </c>
       <c r="S114" t="s">
@@ -9412,7 +9519,7 @@
         <v>992</v>
       </c>
       <c r="I115" t="s">
-        <v>1015</v>
+        <v>993</v>
       </c>
       <c r="M115">
         <v>21.805817448268598</v>
@@ -9421,9 +9528,9 @@
         <v>-102.294075689313</v>
       </c>
       <c r="O115" t="s">
-        <v>985</v>
-      </c>
-      <c r="P115" s="1">
+        <v>986</v>
+      </c>
+      <c r="P115">
         <v>20342</v>
       </c>
       <c r="S115" t="s">
@@ -9435,10 +9542,10 @@
         <v>581</v>
       </c>
       <c r="H116" t="s">
-        <v>1001</v>
+        <v>994</v>
       </c>
       <c r="I116" t="s">
-        <v>1022</v>
+        <v>995</v>
       </c>
       <c r="M116">
         <v>19.2338079716076</v>
@@ -9447,9 +9554,9 @@
         <v>-103.724750218184</v>
       </c>
       <c r="O116" t="s">
-        <v>985</v>
-      </c>
-      <c r="P116" s="1">
+        <v>986</v>
+      </c>
+      <c r="P116">
         <v>28000</v>
       </c>
       <c r="S116" t="s">
@@ -9461,10 +9568,10 @@
         <v>218</v>
       </c>
       <c r="H117" t="s">
-        <v>990</v>
+        <v>996</v>
       </c>
       <c r="I117" t="s">
-        <v>1012</v>
+        <v>997</v>
       </c>
       <c r="M117">
         <v>21.1074262058942</v>
@@ -9473,9 +9580,9 @@
         <v>-101.646580845144</v>
       </c>
       <c r="O117" t="s">
-        <v>985</v>
-      </c>
-      <c r="P117" s="1">
+        <v>986</v>
+      </c>
+      <c r="P117">
         <v>37510</v>
       </c>
       <c r="S117" t="s">
@@ -9487,10 +9594,10 @@
         <v>289</v>
       </c>
       <c r="H118" t="s">
-        <v>989</v>
+        <v>998</v>
       </c>
       <c r="I118" t="s">
-        <v>1011</v>
+        <v>999</v>
       </c>
       <c r="M118">
         <v>20.584004819022201</v>
@@ -9499,9 +9606,9 @@
         <v>-103.35789429928801</v>
       </c>
       <c r="O118" t="s">
-        <v>985</v>
-      </c>
-      <c r="P118" s="1">
+        <v>986</v>
+      </c>
+      <c r="P118">
         <v>45598</v>
       </c>
       <c r="S118" t="s">
@@ -9510,13 +9617,13 @@
     </row>
     <row r="119" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
-        <v>994</v>
+        <v>1000</v>
       </c>
       <c r="H119" t="s">
-        <v>995</v>
+        <v>1001</v>
       </c>
       <c r="I119" t="s">
-        <v>1017</v>
+        <v>1002</v>
       </c>
       <c r="M119">
         <v>19.302520619446501</v>
@@ -9525,9 +9632,9 @@
         <v>-99.611044660511595</v>
       </c>
       <c r="O119" t="s">
-        <v>985</v>
-      </c>
-      <c r="P119" s="1">
+        <v>986</v>
+      </c>
+      <c r="P119">
         <v>50016</v>
       </c>
       <c r="S119" t="s">
@@ -9539,10 +9646,10 @@
         <v>498</v>
       </c>
       <c r="H120" t="s">
-        <v>1013</v>
+        <v>1003</v>
       </c>
       <c r="I120" t="s">
-        <v>1014</v>
+        <v>1004</v>
       </c>
       <c r="M120">
         <v>19.705410396488301</v>
@@ -9551,9 +9658,9 @@
         <v>-99.181866973998794</v>
       </c>
       <c r="O120" t="s">
-        <v>985</v>
-      </c>
-      <c r="P120" s="1">
+        <v>986</v>
+      </c>
+      <c r="P120">
         <v>54713</v>
       </c>
       <c r="S120" t="s">
@@ -9565,10 +9672,10 @@
         <v>316</v>
       </c>
       <c r="H121" t="s">
-        <v>988</v>
+        <v>1005</v>
       </c>
       <c r="I121" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="M121">
         <v>18.9076218307641</v>
@@ -9577,9 +9684,9 @@
         <v>-99.168601360516703</v>
       </c>
       <c r="O121" t="s">
-        <v>985</v>
-      </c>
-      <c r="P121" s="1">
+        <v>986</v>
+      </c>
+      <c r="P121">
         <v>62578</v>
       </c>
       <c r="S121" t="s">
@@ -9588,13 +9695,13 @@
     </row>
     <row r="122" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
-        <v>997</v>
+        <v>1007</v>
       </c>
       <c r="H122" t="s">
-        <v>998</v>
+        <v>1008</v>
       </c>
       <c r="I122" t="s">
-        <v>1019</v>
+        <v>1009</v>
       </c>
       <c r="M122">
         <v>21.474595261228501</v>
@@ -9603,9 +9710,9 @@
         <v>-104.852706118154</v>
       </c>
       <c r="O122" t="s">
-        <v>985</v>
-      </c>
-      <c r="P122" s="1">
+        <v>986</v>
+      </c>
+      <c r="P122">
         <v>63173</v>
       </c>
       <c r="S122" t="s">
@@ -9617,10 +9724,10 @@
         <v>169</v>
       </c>
       <c r="H123" t="s">
-        <v>1005</v>
+        <v>1010</v>
       </c>
       <c r="I123" t="s">
-        <v>1025</v>
+        <v>1011</v>
       </c>
       <c r="M123">
         <v>25.725167783231999</v>
@@ -9629,9 +9736,9 @@
         <v>-100.27377470274099</v>
       </c>
       <c r="O123" t="s">
-        <v>985</v>
-      </c>
-      <c r="P123" s="1">
+        <v>986</v>
+      </c>
+      <c r="P123">
         <v>66480</v>
       </c>
       <c r="S123" t="s">
@@ -9643,10 +9750,10 @@
         <v>263</v>
       </c>
       <c r="H124" t="s">
-        <v>996</v>
+        <v>1012</v>
       </c>
       <c r="I124" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="M124">
         <v>19.111799181770898</v>
@@ -9655,9 +9762,9 @@
         <v>-98.262449560514</v>
       </c>
       <c r="O124" t="s">
-        <v>985</v>
-      </c>
-      <c r="P124" s="1">
+        <v>986</v>
+      </c>
+      <c r="P124">
         <v>72702</v>
       </c>
       <c r="S124" t="s">
@@ -9669,10 +9776,10 @@
         <v>425</v>
       </c>
       <c r="H125" t="s">
-        <v>984</v>
+        <v>1014</v>
       </c>
       <c r="I125" t="s">
-        <v>1007</v>
+        <v>1015</v>
       </c>
       <c r="M125">
         <v>20.572709084345298</v>
@@ -9681,9 +9788,9 @@
         <v>-100.313044045151</v>
       </c>
       <c r="O125" t="s">
-        <v>985</v>
-      </c>
-      <c r="P125" s="1">
+        <v>986</v>
+      </c>
+      <c r="P125">
         <v>76246</v>
       </c>
       <c r="S125" t="s">
@@ -9695,10 +9802,10 @@
         <v>62</v>
       </c>
       <c r="H126" t="s">
-        <v>993</v>
+        <v>1016</v>
       </c>
       <c r="I126" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="M126">
         <v>21.135016545013698</v>
@@ -9707,9 +9814,9 @@
         <v>-86.897355860487096</v>
       </c>
       <c r="O126" t="s">
-        <v>985</v>
-      </c>
-      <c r="P126" s="1">
+        <v>986</v>
+      </c>
+      <c r="P126">
         <v>77536</v>
       </c>
       <c r="S126" t="s">
@@ -9721,10 +9828,10 @@
         <v>452</v>
       </c>
       <c r="H127" t="s">
-        <v>986</v>
+        <v>1018</v>
       </c>
       <c r="I127" t="s">
-        <v>1008</v>
+        <v>1019</v>
       </c>
       <c r="M127">
         <v>22.087116717088701</v>
@@ -9733,9 +9840,9 @@
         <v>-100.876463818144</v>
       </c>
       <c r="O127" t="s">
-        <v>985</v>
-      </c>
-      <c r="P127" s="1">
+        <v>986</v>
+      </c>
+      <c r="P127">
         <v>78421</v>
       </c>
       <c r="S127" t="s">
@@ -9744,13 +9851,13 @@
     </row>
     <row r="128" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
-        <v>1002</v>
+        <v>1020</v>
       </c>
       <c r="H128" t="s">
-        <v>1003</v>
+        <v>1021</v>
       </c>
       <c r="I128" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="M128">
         <v>24.7486679228758</v>
@@ -9759,24 +9866,24 @@
         <v>-107.457388071022</v>
       </c>
       <c r="O128" t="s">
-        <v>985</v>
-      </c>
-      <c r="P128" s="1">
+        <v>986</v>
+      </c>
+      <c r="P128">
         <v>80140</v>
       </c>
       <c r="S128" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="129" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
         <v>922</v>
       </c>
       <c r="H129" t="s">
-        <v>987</v>
+        <v>1023</v>
       </c>
       <c r="I129" t="s">
-        <v>1009</v>
+        <v>1024</v>
       </c>
       <c r="M129">
         <v>18.029792729223502</v>
@@ -9785,24 +9892,24 @@
         <v>-92.909358574019507</v>
       </c>
       <c r="O129" t="s">
-        <v>985</v>
-      </c>
-      <c r="P129" s="1">
+        <v>986</v>
+      </c>
+      <c r="P129">
         <v>86010</v>
       </c>
       <c r="S129" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="130" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
         <v>306</v>
       </c>
       <c r="H130" t="s">
-        <v>999</v>
+        <v>1025</v>
       </c>
       <c r="I130" t="s">
-        <v>1020</v>
+        <v>1026</v>
       </c>
       <c r="M130">
         <v>20.941264484173299</v>
@@ -9811,13 +9918,346 @@
         <v>-89.649069445146296</v>
       </c>
       <c r="O130" t="s">
-        <v>985</v>
-      </c>
-      <c r="P130" s="1">
+        <v>986</v>
+      </c>
+      <c r="P130">
         <v>97260</v>
       </c>
       <c r="S130" t="s">
         <v>63</v>
+      </c>
+    </row>
+    <row r="131" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B131" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C131" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D131" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E131" t="s">
+        <v>184</v>
+      </c>
+      <c r="F131">
+        <v>0</v>
+      </c>
+      <c r="G131" t="s">
+        <v>1031</v>
+      </c>
+      <c r="H131" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I131" t="s">
+        <v>1033</v>
+      </c>
+      <c r="J131" t="s">
+        <v>1034</v>
+      </c>
+      <c r="K131" t="s">
+        <v>1035</v>
+      </c>
+      <c r="L131" t="s">
+        <v>41</v>
+      </c>
+      <c r="M131">
+        <v>22.7660914881242</v>
+      </c>
+      <c r="N131">
+        <v>-102.54222546046201</v>
+      </c>
+      <c r="O131" t="s">
+        <v>28</v>
+      </c>
+      <c r="P131" s="1">
+        <v>98064</v>
+      </c>
+      <c r="R131" t="s">
+        <v>1071</v>
+      </c>
+      <c r="S131" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="132" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B132" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C132" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D132" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E132" t="s">
+        <v>474</v>
+      </c>
+      <c r="F132">
+        <v>0</v>
+      </c>
+      <c r="G132" t="s">
+        <v>1039</v>
+      </c>
+      <c r="H132" t="s">
+        <v>1040</v>
+      </c>
+      <c r="I132" t="s">
+        <v>1041</v>
+      </c>
+      <c r="J132" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K132" t="s">
+        <v>1043</v>
+      </c>
+      <c r="L132" t="s">
+        <v>41</v>
+      </c>
+      <c r="M132">
+        <v>18.894901299312799</v>
+      </c>
+      <c r="N132">
+        <v>-99.0334807048269</v>
+      </c>
+      <c r="O132" t="s">
+        <v>28</v>
+      </c>
+      <c r="P132" s="1">
+        <v>62737</v>
+      </c>
+      <c r="R132" t="s">
+        <v>316</v>
+      </c>
+      <c r="S132" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="133" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B133" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C133" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D133" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E133" t="s">
+        <v>474</v>
+      </c>
+      <c r="F133">
+        <v>0</v>
+      </c>
+      <c r="G133" t="s">
+        <v>1039</v>
+      </c>
+      <c r="H133" t="s">
+        <v>1040</v>
+      </c>
+      <c r="I133" t="s">
+        <v>1041</v>
+      </c>
+      <c r="J133" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K133" t="s">
+        <v>1043</v>
+      </c>
+      <c r="L133" t="s">
+        <v>41</v>
+      </c>
+      <c r="M133">
+        <v>18.894901299312799</v>
+      </c>
+      <c r="N133">
+        <v>-99.0334807048269</v>
+      </c>
+      <c r="O133" t="s">
+        <v>28</v>
+      </c>
+      <c r="P133" s="1">
+        <v>62737</v>
+      </c>
+      <c r="R133" t="s">
+        <v>316</v>
+      </c>
+      <c r="S133" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="134" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B134" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C134" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D134" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E134" t="s">
+        <v>91</v>
+      </c>
+      <c r="F134">
+        <v>0</v>
+      </c>
+      <c r="G134" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H134" t="s">
+        <v>1050</v>
+      </c>
+      <c r="I134" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J134" t="s">
+        <v>1052</v>
+      </c>
+      <c r="K134" t="s">
+        <v>1053</v>
+      </c>
+      <c r="L134" t="s">
+        <v>41</v>
+      </c>
+      <c r="M134">
+        <v>25.705686519644601</v>
+      </c>
+      <c r="N134">
+        <v>-100.239928458447</v>
+      </c>
+      <c r="O134" t="s">
+        <v>28</v>
+      </c>
+      <c r="P134" s="1">
+        <v>66494</v>
+      </c>
+      <c r="R134" t="s">
+        <v>169</v>
+      </c>
+      <c r="S134" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="135" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B135" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C135" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D135" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E135" t="s">
+        <v>401</v>
+      </c>
+      <c r="F135">
+        <v>0</v>
+      </c>
+      <c r="G135" t="s">
+        <v>1057</v>
+      </c>
+      <c r="H135" t="s">
+        <v>1058</v>
+      </c>
+      <c r="I135" t="s">
+        <v>1059</v>
+      </c>
+      <c r="J135" t="s">
+        <v>1060</v>
+      </c>
+      <c r="K135" t="s">
+        <v>1061</v>
+      </c>
+      <c r="L135" t="s">
+        <v>41</v>
+      </c>
+      <c r="M135">
+        <v>19.481043618469801</v>
+      </c>
+      <c r="N135">
+        <v>-99.148506402747103</v>
+      </c>
+      <c r="O135" t="s">
+        <v>28</v>
+      </c>
+      <c r="P135" s="1">
+        <v>7760</v>
+      </c>
+      <c r="R135" t="s">
+        <v>86</v>
+      </c>
+      <c r="S135" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="136" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B136" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C136" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D136" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E136" t="s">
+        <v>91</v>
+      </c>
+      <c r="G136" t="s">
+        <v>1066</v>
+      </c>
+      <c r="H136" t="s">
+        <v>1067</v>
+      </c>
+      <c r="I136" t="s">
+        <v>1068</v>
+      </c>
+      <c r="J136" t="s">
+        <v>1069</v>
+      </c>
+      <c r="K136" t="s">
+        <v>1070</v>
+      </c>
+      <c r="L136" t="s">
+        <v>41</v>
+      </c>
+      <c r="M136">
+        <v>31.611592290876999</v>
+      </c>
+      <c r="N136">
+        <v>-106.34880460447199</v>
+      </c>
+      <c r="O136" t="s">
+        <v>28</v>
+      </c>
+      <c r="P136" s="1">
+        <v>32599</v>
+      </c>
+      <c r="R136" t="s">
+        <v>335</v>
+      </c>
+      <c r="S136" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
